--- a/week 01/Pancafe_survey_results.xlsx
+++ b/week 01/Pancafe_survey_results.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{C5F41793-B564-4374-9C63-61111DB157CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -224,7 +224,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -255,11 +255,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -309,22 +308,22 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1551,13 +1550,13 @@
     <cacheField name="Id" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="8"/>
     </cacheField>
-    <cacheField name="Start time" numFmtId="166">
+    <cacheField name="Start time" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-09T09:22:11" maxDate="2026-04-09T15:49:20"/>
     </cacheField>
-    <cacheField name="Completion time" numFmtId="166">
+    <cacheField name="Completion time" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-09T09:22:50" maxDate="2026-04-09T15:51:11"/>
     </cacheField>
-    <cacheField name="Time To Complete" numFmtId="166">
+    <cacheField name="Time To Complete" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="1899-12-30T00:00:39" maxDate="1899-12-30T00:03:53"/>
     </cacheField>
     <cacheField name="Email" numFmtId="0">
@@ -1708,13 +1707,13 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCDD9D18-08EE-429E-83FF-C0795768A83E}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCDD9D18-08EE-429E-83FF-C0795768A83E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A1:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2211,81 +2210,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2FC9194-AC58-4AC8-B1C9-F0C1D050AAF8}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="77.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>8</v>
       </c>
     </row>
@@ -2298,18 +2297,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
     <col min="3" max="12" width="73" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -2340,17 +2339,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>46121.390405092592</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>46121.390856481485</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f t="shared" ref="D2:D9" si="0">C2-B2</f>
         <v>4.5138889254303649E-4</v>
       </c>
@@ -2373,17 +2372,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>46121.414918981478</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>46121.415486111109</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f t="shared" si="0"/>
         <v>5.671296312357299E-4</v>
       </c>
@@ -2409,17 +2408,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>46121.414652777778</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>46121.417349537034</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f t="shared" si="0"/>
         <v>2.6967592566506937E-3</v>
       </c>
@@ -2445,17 +2444,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>46121.434016203704</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>46121.434710648151</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f t="shared" si="0"/>
         <v>6.944444467080757E-4</v>
       </c>
@@ -2481,17 +2480,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>46121.49596064815</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>46121.498055555552</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f t="shared" si="0"/>
         <v>2.0949074023519643E-3</v>
       </c>
@@ -2517,17 +2516,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>46121.547291666669</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>46121.548113425924</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f t="shared" si="0"/>
         <v>8.2175925490446389E-4</v>
       </c>
@@ -2553,17 +2552,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>46121.612361111111</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>46121.613043981481</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f t="shared" si="0"/>
         <v>6.8287036992842332E-4</v>
       </c>
@@ -2589,58 +2588,57 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>46121.659259259301</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>46121.660543981503</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f t="shared" si="0"/>
         <v>1.2847222023992799E-3</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="2"/>
+      <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
         <f>AVERAGE(D2:D9)</f>
         <v>1.1617476820902084E-3</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
       <c r="J10">
         <f>COUNTIF(J2:J9, "Birthday treat")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="2"/>
+      <c r="K10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
